--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/post FET_HRM-2031-0300/panel_11/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/post FET_HRM-2031-0300/panel_11/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.96987</v>
+        <v>17.76826</v>
       </c>
       <c r="D2" t="n">
-        <v>17.88443</v>
+        <v>17.38359</v>
       </c>
       <c r="E2" t="n">
-        <v>17.63776</v>
+        <v>17.76043</v>
       </c>
       <c r="F2" t="n">
-        <v>45.98914</v>
+        <v>45.06189</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05421</v>
+        <v>0.05333</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9408</v>
+        <v>1.93972</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.61579</v>
+        <v>17.85582</v>
       </c>
       <c r="D3" t="n">
-        <v>17.70429</v>
+        <v>17.71042</v>
       </c>
       <c r="E3" t="n">
-        <v>17.51889</v>
+        <v>17.81786</v>
       </c>
       <c r="F3" t="n">
-        <v>44.78064</v>
+        <v>45.37689</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05402</v>
+        <v>0.05411</v>
       </c>
       <c r="H3" t="n">
-        <v>1.93449</v>
+        <v>1.96283</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.71449</v>
+        <v>17.79531</v>
       </c>
       <c r="D4" t="n">
-        <v>17.21726</v>
+        <v>17.60421</v>
       </c>
       <c r="E4" t="n">
-        <v>18.02204</v>
+        <v>17.71418</v>
       </c>
       <c r="F4" t="n">
-        <v>46.10837</v>
+        <v>44.67409</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05472</v>
+        <v>0.05231</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9368</v>
+        <v>1.92923</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.5953</v>
+        <v>17.79157</v>
       </c>
       <c r="D6" t="n">
-        <v>17.04397</v>
+        <v>16.76485</v>
       </c>
       <c r="E6" t="n">
-        <v>17.33819</v>
+        <v>17.41895</v>
       </c>
       <c r="F6" t="n">
-        <v>23.08426</v>
+        <v>22.55729</v>
       </c>
       <c r="G6" t="n">
-        <v>36.1695</v>
+        <v>36.39807</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.75448</v>
+        <v>17.71566</v>
       </c>
       <c r="D7" t="n">
-        <v>16.91468</v>
+        <v>17.06602</v>
       </c>
       <c r="E7" t="n">
-        <v>17.48534</v>
+        <v>17.20385</v>
       </c>
       <c r="F7" t="n">
-        <v>22.87855</v>
+        <v>23.61094</v>
       </c>
       <c r="G7" t="n">
-        <v>35.84462</v>
+        <v>35.95098</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.93215</v>
+        <v>17.58505</v>
       </c>
       <c r="D8" t="n">
-        <v>16.93074</v>
+        <v>17.18149</v>
       </c>
       <c r="E8" t="n">
-        <v>17.62137</v>
+        <v>17.38915</v>
       </c>
       <c r="F8" t="n">
-        <v>23.03675</v>
+        <v>23.11026</v>
       </c>
       <c r="G8" t="n">
-        <v>35.84378</v>
+        <v>35.74561</v>
       </c>
     </row>
   </sheetData>
